--- a/docs/思晨五金-网站文案填写表.xlsx
+++ b/docs/思晨五金-网站文案填写表.xlsx
@@ -1,39 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CF98C4-94BE-4EB5-89E0-707E7CEA18A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="4524" yWindow="720" windowWidth="14208" windowHeight="11640" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="填写说明" sheetId="1" r:id="rId1"/>
-    <sheet name="1-首页文案" sheetId="2" r:id="rId2"/>
-    <sheet name="2-关于我们" sheetId="3" r:id="rId3"/>
-    <sheet name="3-产品中心" sheetId="4" r:id="rId4"/>
-    <sheet name="4-新闻资讯" sheetId="5" r:id="rId5"/>
-    <sheet name="5-联系与页脚" sheetId="6" r:id="rId6"/>
-    <sheet name="6-SEO设置" sheetId="7" r:id="rId7"/>
-    <sheet name="7-图片清单" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="填写说明" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="1-首页文案" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="2-关于我们" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="3-产品中心" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="4-车间概貌" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="5-联系与页脚" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="6-SEO设置" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="7-图片清单" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="384">
   <si>
     <t>这是什么</t>
   </si>
@@ -44,12 +29,15 @@
     <t>怎么填</t>
   </si>
   <si>
-    <t>按 Sheet 顺序（首页 → 关于我们 → 产品中心 → 新闻资讯 → 联系与页脚 → SEO）。留空的字段表示保持现状。</t>
+    <t>按 Sheet 顺序（首页 → 关于我们 → 产品中心 → 车间概貌 → 联系与页脚 → SEO）。留空的字段表示保持现状。</t>
   </si>
   <si>
     <t>带"务必真实"的字段</t>
   </si>
   <si>
+    <t>地址、电话、邮箱、成立年份、备案号——这些不能编造，请填公司真实信息。</t>
+  </si>
+  <si>
     <t>英文名规范</t>
   </si>
   <si>
@@ -83,7 +71,13 @@
     <t>填完怎么发布</t>
   </si>
   <si>
-    <t>告诉我就行，我会执行 npm run publish 一键构建并上传到腾讯云 COS 桶。</t>
+    <t>告诉我就行，我会构建并推送到 GitHub（EdgeOne Pages 会自动部署上线）；需要时可同时上传到 COS 备份。</t>
+  </si>
+  <si>
+    <t>车间图片说明</t>
+  </si>
+  <si>
+    <t>车间概貌每个车间 3 张图：xxx-1 为页面大图，xxx-2 / xxx-3 为细节图（方块数即序号）。</t>
   </si>
   <si>
     <t>咨询</t>
@@ -323,13 +317,43 @@
     <t>说明 30~60 字</t>
   </si>
   <si>
-    <t>首页 · 新闻动态</t>
-  </si>
-  <si>
-    <t>区块标题</t>
-  </si>
-  <si>
-    <t>新闻动态</t>
+    <t>首页 · 车间概貌</t>
+  </si>
+  <si>
+    <t>区块标题 / 说明 / 按钮</t>
+  </si>
+  <si>
+    <t>车间概貌 / 冷镦、CNC、搓牙、光学筛选四大车间，覆盖从毛坯成型到全检出货的完整工序。 / 查看全部车间</t>
+  </si>
+  <si>
+    <t>首页 · 车间卡片 1</t>
+  </si>
+  <si>
+    <t>车间名 / 英文标 / 一句话摘要</t>
+  </si>
+  <si>
+    <t>冷镦车间 / COLD HEADING / 多工位冷镦一次成型，材料利用率高、强度好，适合螺栓螺母与异形件的批量生产。</t>
+  </si>
+  <si>
+    <t>摘要 30~50 字</t>
+  </si>
+  <si>
+    <t>首页 · 车间卡片 2</t>
+  </si>
+  <si>
+    <t>CNC 车间 / CNC MACHINING / 数控车床与加工中心，支持车铣复合加工，精度可达 ±0.01 mm。</t>
+  </si>
+  <si>
+    <t>首页 · 车间卡片 3</t>
+  </si>
+  <si>
+    <t>搓牙车间 / THREAD ROLLING / 螺纹滚压成型，牙型饱满、表面光洁，螺纹强度优于切削加工。</t>
+  </si>
+  <si>
+    <t>首页 · 车间卡片 4</t>
+  </si>
+  <si>
+    <t>光学筛选车间 / OPTICAL SORTING / 光学影像全检，自动剔除尺寸超差、混料、毛刺等不良品。</t>
   </si>
   <si>
     <t>首页 · 底部号召区</t>
@@ -602,67 +626,82 @@
     <t>有图纸或需求？欢迎询价 / 提供图纸或样品，我们将尽快为您评估工艺与报价。 / 发起询价</t>
   </si>
   <si>
-    <t>新闻 · 页首</t>
-  </si>
-  <si>
-    <t>了解思晨的最新动态，以及五金制造行业的前沿信息。</t>
-  </si>
-  <si>
-    <t>新闻 · 头条</t>
-  </si>
-  <si>
-    <t>标题</t>
-  </si>
-  <si>
-    <t>思晨五金通过 ISO9001 质量管理体系年度审核</t>
-  </si>
-  <si>
-    <t>12~28 字</t>
-  </si>
-  <si>
-    <t>分类 / 日期 / 摘要</t>
-  </si>
-  <si>
-    <t>企业新闻 / 2025-06-18 / （现为长摘要，建议 80~140 字）</t>
-  </si>
-  <si>
-    <t>摘要 80~140 字</t>
-  </si>
-  <si>
-    <t>新闻 · 列表 1</t>
-  </si>
-  <si>
-    <t>标题 / 分类 / 日期 / 摘要</t>
-  </si>
-  <si>
-    <t>公司精密冲压自动化产线完成升级改造 / 企业新闻 / 2025-05-30</t>
-  </si>
-  <si>
-    <t>摘要 40~80 字</t>
-  </si>
-  <si>
-    <t>新闻 · 列表 2</t>
-  </si>
-  <si>
-    <t>2025 上半年五金行业景气度观察 / 行业动态 / 2025-05-12</t>
-  </si>
-  <si>
-    <t>新闻 · 列表 3</t>
-  </si>
-  <si>
-    <t>思晨五金参加华南国际工业博览会 / 展会动态 / 2025-04-08</t>
-  </si>
-  <si>
-    <t>新闻 · 列表 4</t>
-  </si>
-  <si>
-    <t>新引进五轴联动加工中心，精密加工能力再升级 / 企业新闻 / 2025-03-21</t>
-  </si>
-  <si>
-    <t>新闻 · 列表 5</t>
-  </si>
-  <si>
-    <t>关于不锈钢紧固件防腐性能的几点建议 / 技术分享 / 2025-02-27</t>
+    <t>车间概貌 · 页首</t>
+  </si>
+  <si>
+    <t>页面标题 / 副标题</t>
+  </si>
+  <si>
+    <t>车间概貌 / 冷镦、CNC、搓牙、光学筛选四大车间，覆盖从毛坯成型到全检出货的完整工序。</t>
+  </si>
+  <si>
+    <t>副标题 30~60 字</t>
+  </si>
+  <si>
+    <t>车间概貌 · 冷镦车间</t>
+  </si>
+  <si>
+    <t>标题 / 英文标</t>
+  </si>
+  <si>
+    <t>冷镦车间 / COLD HEADING WORKSHOP</t>
+  </si>
+  <si>
+    <t>车间描述</t>
+  </si>
+  <si>
+    <t>采用多工位冷镦成型工艺，从盘料一次成型螺栓、螺母及各类异形件。材料利用率高、生产效率快，金属流线连续不断，产品强度与一致性明显优于切削加工。</t>
+  </si>
+  <si>
+    <t>参数 1~4：标签 / 内容（现均为占位）</t>
+  </si>
+  <si>
+    <t>主要设备 / 加工范围 / 日产能 / 品质管控</t>
+  </si>
+  <si>
+    <t>每项 10~30 字</t>
+  </si>
+  <si>
+    <t>车间概貌 · CNC 车间</t>
+  </si>
+  <si>
+    <t>CNC 车间 / CNC MACHINING WORKSHOP</t>
+  </si>
+  <si>
+    <t>配置数控车床与加工中心，支持车铣复合加工，适合结构复杂、公差要求严格的产品；小批量多品种与批量订单均可灵活承接。</t>
+  </si>
+  <si>
+    <t>主要设备 / 加工精度 / 适用材质 / 交付形式</t>
+  </si>
+  <si>
+    <t>车间概貌 · 搓牙车间</t>
+  </si>
+  <si>
+    <t>搓牙车间 / THREAD ROLLING WORKSHOP</t>
+  </si>
+  <si>
+    <t>通过搓丝机对工件进行螺纹滚压成型，牙型饱满、表面光洁，螺纹强度较切削加工显著提升，适合大批量标准紧固件的稳定生产。</t>
+  </si>
+  <si>
+    <t>主要设备 / 螺纹范围 / 日产能 / 检测方式</t>
+  </si>
+  <si>
+    <t>车间概貌 · 光学筛选车间</t>
+  </si>
+  <si>
+    <t>光学筛选车间 / OPTICAL SORTING WORKSHOP</t>
+  </si>
+  <si>
+    <t>采用光学影像筛选设备对产品进行全检，自动剔除尺寸超差、混料、毛刺、缺料等不良品，为出货品质提供最后一道保障。</t>
+  </si>
+  <si>
+    <t>主要设备 / 筛选项目 / 筛选速度 / 质量目标</t>
+  </si>
+  <si>
+    <t>车间概貌 · 底部号召区</t>
+  </si>
+  <si>
+    <t>欢迎实地考察我们的产线 / 如需了解设备清单、产能排期或安排样品试制，欢迎随时联系我们。 / 联系我们</t>
   </si>
   <si>
     <t>联系我们 · 页首</t>
@@ -677,6 +716,9 @@
     <t>公司地址（务必真实）</t>
   </si>
   <si>
+    <t>广东省 XXXXX 工业园区 XX 号（占位）</t>
+  </si>
+  <si>
     <t>详细地址</t>
   </si>
   <si>
@@ -791,10 +833,10 @@
     <t>产品中心 / 思晨五金产品中心——精密冲压件、精密CNC加工件、紧固件、钣金件、模具设计与表面处理服务。</t>
   </si>
   <si>
-    <t>SEO · 新闻资讯</t>
-  </si>
-  <si>
-    <t>新闻资讯 / 思晨五金新闻资讯——企业新闻、行业动态、展会信息与技术分享。</t>
+    <t>SEO · 车间概貌</t>
+  </si>
+  <si>
+    <t>车间概貌 / 思晨五金车间概貌——冷镦车间、CNC 车间、搓牙车间、光学筛选车间，覆盖从成型到全检的完整五金制造工序。</t>
   </si>
   <si>
     <t>SEO · 联系我们</t>
@@ -815,6 +857,12 @@
     <t>1600×900</t>
   </si>
   <si>
+    <t>slider-2.png</t>
+  </si>
+  <si>
+    <t>首页 · 公司概貌轮播图【第 2 张】生产车间全景</t>
+  </si>
+  <si>
     <t>slider-3.png</t>
   </si>
   <si>
@@ -1046,129 +1094,113 @@
     <t>关于我们 · 证书展示 第 6 张</t>
   </si>
   <si>
-    <t>news（新闻）</t>
-  </si>
-  <si>
-    <t>news-1.png</t>
-  </si>
-  <si>
-    <t>新闻 · 头条配图</t>
-  </si>
-  <si>
-    <t>1280×720</t>
-  </si>
-  <si>
-    <t>news-2.png</t>
-  </si>
-  <si>
-    <t>首页新闻卡 1 / 新闻列表 1</t>
-  </si>
-  <si>
-    <t>news-3.png</t>
-  </si>
-  <si>
-    <t>首页新闻卡 2 / 新闻列表 2</t>
-  </si>
-  <si>
-    <t>news-4.png</t>
-  </si>
-  <si>
-    <t>首页新闻卡 3 / 新闻列表 3</t>
-  </si>
-  <si>
-    <t>news-5.png</t>
-  </si>
-  <si>
-    <t>新闻列表 4</t>
-  </si>
-  <si>
-    <t>news-6.png</t>
-  </si>
-  <si>
-    <t>新闻列表 5</t>
+    <t>workshops（车间）</t>
+  </si>
+  <si>
+    <t>cold-heading-1.png</t>
+  </si>
+  <si>
+    <t>车间概貌 · 冷镦车间【大图】</t>
+  </si>
+  <si>
+    <t>cold-heading-2.png</t>
+  </si>
+  <si>
+    <t>冷镦车间 · 细节图 1</t>
+  </si>
+  <si>
+    <t>cold-heading-3.png</t>
+  </si>
+  <si>
+    <t>冷镦车间 · 细节图 2</t>
+  </si>
+  <si>
+    <t>cnc-1.png</t>
+  </si>
+  <si>
+    <t>车间概貌 · CNC 车间【大图】</t>
+  </si>
+  <si>
+    <t>cnc-2.png</t>
+  </si>
+  <si>
+    <t>CNC 车间 · 细节图 1</t>
+  </si>
+  <si>
+    <t>cnc-3.png</t>
+  </si>
+  <si>
+    <t>CNC 车间 · 细节图 2</t>
+  </si>
+  <si>
+    <t>thread-rolling-1.png</t>
+  </si>
+  <si>
+    <t>车间概貌 · 搓牙车间【大图】</t>
+  </si>
+  <si>
+    <t>thread-rolling-2.png</t>
+  </si>
+  <si>
+    <t>搓牙车间 · 细节图 1</t>
+  </si>
+  <si>
+    <t>thread-rolling-3.png</t>
+  </si>
+  <si>
+    <t>搓牙车间 · 细节图 2</t>
+  </si>
+  <si>
+    <t>optical-sorting-1.png</t>
+  </si>
+  <si>
+    <t>车间概貌 · 光学筛选车间【大图】</t>
+  </si>
+  <si>
+    <t>optical-sorting-2.png</t>
+  </si>
+  <si>
+    <t>光学筛选车间 · 细节图 1</t>
+  </si>
+  <si>
+    <t>optical-sorting-3.png</t>
+  </si>
+  <si>
+    <t>光学筛选车间 · 细节图 2</t>
   </si>
   <si>
     <t>提示：直接把真实图片按"文件名"放入对应目录覆盖即可，无需改动代码。</t>
-  </si>
-  <si>
-    <t>地址、电话、邮箱、成立年份、备案号——这些不能编造，请填公司真实信息。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>广东省 XXXXX 工业园区 XX 号（占位）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>粤ICP备2026136130号</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>广东省中山市三乡镇第二工业区皇冠路5号8栋之A区</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>首页 · 公司概貌轮播图【第 2 张】生产车间全景</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>slider-2.png</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <i/>
-      <sz val="11"/>
       <color rgb="FF7A7A7A"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1185,12 +1217,6 @@
         <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1204,7 +1230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1220,13 +1246,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1562,15 +1584,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1578,7 +1600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1586,89 +1608,96 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1678,24 +1707,24 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1703,19 +1732,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1723,39 +1752,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1763,19 +1792,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1783,379 +1812,379 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F17" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F21" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2163,19 +2192,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2183,55 +2212,134 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F26" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
+      <c r="B31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2241,440 +2349,439 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2684,360 +2791,359 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3047,24 +3153,24 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3072,19 +3178,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>104</v>
+        <v>203</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3092,418 +3198,274 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>197</v>
+        <v>51</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>30</v>
+      <c r="D10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3513,24 +3475,24 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3538,135 +3500,234 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>30</v>
+      <c r="F12" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3676,24 +3737,24 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3701,19 +3762,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3721,19 +3782,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>357</v>
+        <v>262</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>356</v>
+        <v>263</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3741,19 +3802,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3761,19 +3822,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3781,19 +3842,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3801,19 +3862,181 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>268</v>
       </c>
+      <c r="F7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3821,199 +4044,199 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="F16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4021,19 +4244,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4041,19 +4264,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4061,19 +4284,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4081,19 +4304,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4101,19 +4324,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4121,19 +4344,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4141,19 +4364,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4161,19 +4384,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4181,19 +4404,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4201,19 +4424,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4221,19 +4444,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4241,19 +4464,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4261,19 +4484,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4281,19 +4504,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4301,19 +4524,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4321,139 +4544,139 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4461,19 +4684,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>340</v>
+        <v>278</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4481,19 +4704,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4501,19 +4724,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4521,19 +4744,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>340</v>
+        <v>278</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4541,19 +4764,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4561,29 +4784,148 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>351</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/docs/思晨五金-网站文案填写表.xlsx
+++ b/docs/思晨五金-网站文案填写表.xlsx
@@ -71,7 +71,7 @@
     <t>填完怎么发布</t>
   </si>
   <si>
-    <t>告诉我就行，我会构建并推送到 GitHub（EdgeOne Pages 会自动部署上线）；需要时可同时上传到 COS 备份。</t>
+    <t>告诉我就行，我会构建并推送到 GitHub（EdgeOne Pages 会自动部署上线）。</t>
   </si>
   <si>
     <t>车间图片说明</t>

--- a/docs/思晨五金-网站文案填写表.xlsx
+++ b/docs/思晨五金-网站文案填写表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="388">
   <si>
     <t>这是什么</t>
   </si>
@@ -713,19 +713,19 @@
     <t>联系我们 · 联系方式</t>
   </si>
   <si>
-    <t>公司地址（务必真实）</t>
-  </si>
-  <si>
-    <t>广东省 XXXXX 工业园区 XX 号（占位）</t>
-  </si>
-  <si>
-    <t>详细地址</t>
+    <t>公司地址（已填真实地址）</t>
+  </si>
+  <si>
+    <t>广东省中山市三乡镇第二工业区皇冠路5号8栋之A区</t>
+  </si>
+  <si>
+    <t>如需微调请在此列覆盖</t>
   </si>
   <si>
     <t>联系电话（务必真实）</t>
   </si>
   <si>
-    <t>+86 0757-XXXX-XXXX（占位）</t>
+    <t>+86 0760-XXXX-XXXX（占位，中山区号 0760）</t>
   </si>
   <si>
     <t>含区号</t>
@@ -758,7 +758,10 @@
     <t>联系我们 · 地图</t>
   </si>
   <si>
-    <t>地图占位——上线后可替换为高德 / 腾讯地图 iframe 嵌入。</t>
+    <t>区块说明 / 地址</t>
+  </si>
+  <si>
+    <t>公司位置（地址已填真实）：广东省中山市三乡镇第二工业区皇冠路5号8栋之A区；提供高德/百度一键导航按钮</t>
   </si>
   <si>
     <t>页脚</t>
@@ -894,6 +897,15 @@
   </si>
   <si>
     <t>关于我们 · 公司风采（团队合影）</t>
+  </si>
+  <si>
+    <t>map-1.png</t>
+  </si>
+  <si>
+    <t>联系我们 · 公司位置示意图（可换成地图 App 位置截图）</t>
+  </si>
+  <si>
+    <t>1920×800</t>
   </si>
   <si>
     <t>equipment（器械设备）</t>
@@ -3623,10 +3635,10 @@
         <v>245</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>246</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>170</v>
@@ -3640,13 +3652,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>54</v>
@@ -3660,16 +3672,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>33</v>
@@ -3680,16 +3692,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>33</v>
@@ -3700,16 +3712,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>33</v>
@@ -3762,16 +3774,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>33</v>
@@ -3782,16 +3794,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>33</v>
@@ -3802,16 +3814,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
@@ -3822,16 +3834,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
@@ -3842,16 +3854,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -3862,16 +3874,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>33</v>
@@ -3888,7 +3900,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3924,16 +3936,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>33</v>
@@ -3944,16 +3956,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>33</v>
@@ -3964,16 +3976,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
@@ -3984,16 +3996,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
@@ -4004,16 +4016,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -4024,16 +4036,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>33</v>
@@ -4044,16 +4056,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>33</v>
@@ -4064,7 +4076,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>293</v>
@@ -4084,16 +4096,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>33</v>
@@ -4104,16 +4116,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>33</v>
@@ -4124,16 +4136,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>33</v>
@@ -4144,16 +4156,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>33</v>
@@ -4164,16 +4176,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>33</v>
@@ -4184,16 +4196,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>33</v>
@@ -4204,16 +4216,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>33</v>
@@ -4224,16 +4236,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>33</v>
@@ -4244,16 +4256,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>33</v>
@@ -4264,16 +4276,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>33</v>
@@ -4284,16 +4296,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>33</v>
@@ -4304,16 +4316,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
@@ -4324,16 +4336,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -4344,16 +4356,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>33</v>
@@ -4364,16 +4376,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>33</v>
@@ -4384,16 +4396,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>33</v>
@@ -4404,16 +4416,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>33</v>
@@ -4424,16 +4436,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>33</v>
@@ -4444,16 +4456,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>33</v>
@@ -4464,16 +4476,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>33</v>
@@ -4484,16 +4496,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -4504,16 +4516,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
@@ -4524,16 +4536,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
@@ -4544,16 +4556,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>33</v>
@@ -4564,16 +4576,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
@@ -4584,16 +4596,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
@@ -4604,16 +4616,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
@@ -4624,16 +4636,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
@@ -4644,16 +4656,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>33</v>
@@ -4664,16 +4676,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>33</v>
@@ -4684,16 +4696,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -4704,16 +4716,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>33</v>
@@ -4724,16 +4736,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>33</v>
@@ -4744,16 +4756,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>33</v>
@@ -4764,16 +4776,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>33</v>
@@ -4784,16 +4796,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>33</v>
@@ -4804,16 +4816,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>33</v>
@@ -4824,16 +4836,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>33</v>
@@ -4844,16 +4856,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>33</v>
@@ -4864,16 +4876,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>33</v>
@@ -4884,16 +4896,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>33</v>
@@ -4904,24 +4916,44 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>383</v>
+    <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/docs/思晨五金-网站文案填写表.xlsx
+++ b/docs/思晨五金-网站文案填写表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="391">
   <si>
     <t>这是什么</t>
   </si>
@@ -722,13 +722,13 @@
     <t>如需微调请在此列覆盖</t>
   </si>
   <si>
-    <t>联系电话（务必真实）</t>
-  </si>
-  <si>
-    <t>+86 0760-XXXX-XXXX（占位，中山区号 0760）</t>
-  </si>
-  <si>
-    <t>含区号</t>
+    <t>联系电话（已填真实号码）</t>
+  </si>
+  <si>
+    <t>139 2818 0479（可点击拨打）</t>
+  </si>
+  <si>
+    <t>如需更换请覆盖</t>
   </si>
   <si>
     <t>电子邮箱（务必真实）</t>
@@ -851,48 +851,51 @@
     <t>company（公司）</t>
   </si>
   <si>
-    <t>slider-1.png</t>
-  </si>
-  <si>
-    <t>首页 · 公司概貌轮播图【第 1 张】厂区外景</t>
+    <t>slider-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 首页轮播图【第 1 张】厂区外景</t>
+  </si>
+  <si>
+    <t>1600px</t>
+  </si>
+  <si>
+    <t>slider-2.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 首页轮播图【第 2 张】生产车间全景</t>
+  </si>
+  <si>
+    <t>slider-3.png</t>
+  </si>
+  <si>
+    <t>首页 · 公司概貌轮播图【第 3 张】办公与展厅（待替换）</t>
   </si>
   <si>
     <t>1600×900</t>
   </si>
   <si>
-    <t>slider-2.png</t>
-  </si>
-  <si>
-    <t>首页 · 公司概貌轮播图【第 2 张】生产车间全景</t>
-  </si>
-  <si>
-    <t>slider-3.png</t>
-  </si>
-  <si>
-    <t>首页 · 公司概貌轮播图【第 3 张】办公与展厅</t>
-  </si>
-  <si>
     <t>slider-4.png</t>
   </si>
   <si>
-    <t>首页 · 公司概貌轮播图【第 4 张】团队与品质</t>
-  </si>
-  <si>
-    <t>facade.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 公司外景 / 办公环境</t>
+    <t>首页 · 公司概貌轮播图【第 4 张】团队与品质（待替换）</t>
+  </si>
+  <si>
+    <t>facade.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 公司外景 / 办公环境</t>
+  </si>
+  <si>
+    <t>office-1.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 公司风采（办公与展厅）</t>
   </si>
   <si>
     <t>1200×900</t>
   </si>
   <si>
-    <t>office-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 公司风采（办公与展厅）</t>
-  </si>
-  <si>
     <t>team-1.png</t>
   </si>
   <si>
@@ -911,13 +914,13 @@
     <t>equipment（器械设备）</t>
   </si>
   <si>
-    <t>hero.png</t>
-  </si>
-  <si>
-    <t>首页首屏大图（建议宽幅厂房/设备大图）</t>
-  </si>
-  <si>
-    <t>1920×1080</t>
+    <t>hero.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 首页首屏大图</t>
+  </si>
+  <si>
+    <t>1920px</t>
   </si>
   <si>
     <t>workshop-1.png</t>
@@ -938,34 +941,37 @@
     <t>关于我们 · 工厂与设备（CNC 车间）</t>
   </si>
   <si>
-    <t>lab-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 工厂与设备（品质检测中心）</t>
-  </si>
-  <si>
-    <t>machine-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 工厂与设备（生产设备 1）</t>
-  </si>
-  <si>
-    <t>machine-2.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 工厂与设备（生产设备 2）</t>
-  </si>
-  <si>
-    <t>qc-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 工厂与设备（品质管控）</t>
+    <t>lab-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（品质检测中心）</t>
+  </si>
+  <si>
+    <t>1400px</t>
+  </si>
+  <si>
+    <t>machine-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（生产设备 1）</t>
+  </si>
+  <si>
+    <t>machine-2.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（生产设备 2）</t>
+  </si>
+  <si>
+    <t>qc-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（品质管控）</t>
   </si>
   <si>
     <t>warehouse-1.png</t>
   </si>
   <si>
-    <t>关于我们 · 工厂与设备（仓储物流）</t>
+    <t>关于我们 · 工厂与设备（仓储物流，待替换）</t>
   </si>
   <si>
     <t>products（产品）</t>
@@ -1109,76 +1115,79 @@
     <t>workshops（车间）</t>
   </si>
   <si>
-    <t>cold-heading-1.png</t>
-  </si>
-  <si>
-    <t>车间概貌 · 冷镦车间【大图】</t>
+    <t>cold-heading-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 车间概貌 · 冷镦车间【大图】</t>
   </si>
   <si>
     <t>cold-heading-2.png</t>
   </si>
   <si>
-    <t>冷镦车间 · 细节图 1</t>
+    <t>冷镦车间 · 细节图 1（待替换）</t>
   </si>
   <si>
     <t>cold-heading-3.png</t>
   </si>
   <si>
-    <t>冷镦车间 · 细节图 2</t>
-  </si>
-  <si>
-    <t>cnc-1.png</t>
-  </si>
-  <si>
-    <t>车间概貌 · CNC 车间【大图】</t>
-  </si>
-  <si>
-    <t>cnc-2.png</t>
-  </si>
-  <si>
-    <t>CNC 车间 · 细节图 1</t>
-  </si>
-  <si>
-    <t>cnc-3.png</t>
-  </si>
-  <si>
-    <t>CNC 车间 · 细节图 2</t>
+    <t>冷镦车间 · 细节图 2（待替换）</t>
+  </si>
+  <si>
+    <t>cnc-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 车间概貌 · CNC 车间【大图】</t>
+  </si>
+  <si>
+    <t>cnc-2.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · CNC 车间 · 细节图 1</t>
+  </si>
+  <si>
+    <t>1200px</t>
+  </si>
+  <si>
+    <t>cnc-3.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · CNC 车间 · 细节图 2</t>
   </si>
   <si>
     <t>thread-rolling-1.png</t>
   </si>
   <si>
-    <t>车间概貌 · 搓牙车间【大图】</t>
+    <t>车间概貌 · 搓牙车间【大图】（待替换）</t>
   </si>
   <si>
     <t>thread-rolling-2.png</t>
   </si>
   <si>
-    <t>搓牙车间 · 细节图 1</t>
+    <t>搓牙车间 · 细节图 1（待替换）</t>
   </si>
   <si>
     <t>thread-rolling-3.png</t>
   </si>
   <si>
-    <t>搓牙车间 · 细节图 2</t>
-  </si>
-  <si>
-    <t>optical-sorting-1.png</t>
-  </si>
-  <si>
-    <t>车间概貌 · 光学筛选车间【大图】</t>
+    <t>搓牙车间 · 细节图 2（待替换）</t>
+  </si>
+  <si>
+    <t>optical-sorting-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 车间概貌 · 光学筛选车间【大图】</t>
   </si>
   <si>
     <t>optical-sorting-2.png</t>
   </si>
   <si>
-    <t>光学筛选车间 · 细节图 1</t>
+    <t>光学筛选车间 · 细节图 1（待替换）</t>
   </si>
   <si>
     <t>optical-sorting-3.png</t>
   </si>
   <si>
-    <t>光学筛选车间 · 细节图 2</t>
+    <t>光学筛选车间 · 细节图 2（待替换）</t>
   </si>
   <si>
     <t>提示：直接把真实图片按"文件名"放入对应目录覆盖即可，无需改动代码。</t>
@@ -3985,7 +3994,7 @@
         <v>283</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
@@ -3999,13 +4008,13 @@
         <v>276</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
@@ -4019,13 +4028,13 @@
         <v>276</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -4045,7 +4054,7 @@
         <v>290</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>33</v>
@@ -4059,13 +4068,13 @@
         <v>276</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>33</v>
@@ -4079,13 +4088,13 @@
         <v>276</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>33</v>
@@ -4096,16 +4105,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>33</v>
@@ -4116,16 +4125,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>33</v>
@@ -4136,16 +4145,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>33</v>
@@ -4156,16 +4165,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>33</v>
@@ -4176,16 +4185,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>33</v>
@@ -4196,16 +4205,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>33</v>
@@ -4216,16 +4225,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>33</v>
@@ -4236,16 +4245,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>33</v>
@@ -4256,16 +4265,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>33</v>
@@ -4276,16 +4285,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>33</v>
@@ -4296,16 +4305,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>33</v>
@@ -4316,16 +4325,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
@@ -4336,16 +4345,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -4356,16 +4365,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>33</v>
@@ -4376,16 +4385,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>33</v>
@@ -4396,16 +4405,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>33</v>
@@ -4416,16 +4425,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>33</v>
@@ -4436,16 +4445,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>33</v>
@@ -4456,16 +4465,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>33</v>
@@ -4476,16 +4485,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>33</v>
@@ -4496,16 +4505,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -4516,16 +4525,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
@@ -4536,16 +4545,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
@@ -4556,16 +4565,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>33</v>
@@ -4576,16 +4585,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
@@ -4596,16 +4605,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
@@ -4616,16 +4625,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
@@ -4636,16 +4645,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
@@ -4656,16 +4665,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>33</v>
@@ -4676,16 +4685,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>33</v>
@@ -4696,16 +4705,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -4716,13 +4725,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>279</v>
@@ -4736,16 +4745,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>33</v>
@@ -4756,16 +4765,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>33</v>
@@ -4776,13 +4785,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>279</v>
@@ -4796,16 +4805,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>288</v>
+        <v>375</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>33</v>
@@ -4816,16 +4825,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>288</v>
+        <v>375</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>33</v>
@@ -4836,16 +4845,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>33</v>
@@ -4856,16 +4865,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>33</v>
@@ -4876,16 +4885,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>33</v>
@@ -4896,13 +4905,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>279</v>
@@ -4916,16 +4925,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>33</v>
@@ -4936,16 +4945,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>33</v>
@@ -4953,7 +4962,7 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/docs/思晨五金-网站文案填写表.xlsx
+++ b/docs/思晨五金-网站文案填写表.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DD2810-F608-422F-94A1-0297B290D65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="732" yWindow="384" windowWidth="18348" windowHeight="11640" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="填写说明" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="1-首页文案" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="2-关于我们" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="3-产品中心" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="4-车间概貌" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="5-联系与页脚" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="6-SEO设置" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="7-图片清单" state="visible" r:id="rId11"/>
+    <sheet name="填写说明" sheetId="1" r:id="rId1"/>
+    <sheet name="1-首页文案" sheetId="2" r:id="rId2"/>
+    <sheet name="2-关于我们" sheetId="3" r:id="rId3"/>
+    <sheet name="3-产品中心" sheetId="4" r:id="rId4"/>
+    <sheet name="4-车间概貌" sheetId="5" r:id="rId5"/>
+    <sheet name="5-联系与页脚" sheetId="6" r:id="rId6"/>
+    <sheet name="6-SEO设置" sheetId="7" r:id="rId7"/>
+    <sheet name="7-图片清单" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -632,593 +636,612 @@
     <t>页面标题 / 副标题</t>
   </si>
   <si>
+    <t>副标题 30~60 字</t>
+  </si>
+  <si>
+    <t>车间概貌 · 冷镦车间</t>
+  </si>
+  <si>
+    <t>标题 / 英文标</t>
+  </si>
+  <si>
+    <t>冷镦车间 / COLD HEADING WORKSHOP</t>
+  </si>
+  <si>
+    <t>车间描述</t>
+  </si>
+  <si>
+    <t>采用多工位冷镦成型工艺，从盘料一次成型螺栓、螺母及各类异形件。材料利用率高、生产效率快，金属流线连续不断，产品强度与一致性明显优于切削加工。</t>
+  </si>
+  <si>
+    <t>参数 1~4：标签 / 内容（现均为占位）</t>
+  </si>
+  <si>
+    <t>主要设备 / 加工范围 / 日产能 / 品质管控</t>
+  </si>
+  <si>
+    <t>每项 10~30 字</t>
+  </si>
+  <si>
+    <t>车间概貌 · CNC 车间</t>
+  </si>
+  <si>
+    <t>CNC 车间 / CNC MACHINING WORKSHOP</t>
+  </si>
+  <si>
+    <t>配置数控车床与加工中心，支持车铣复合加工，适合结构复杂、公差要求严格的产品；小批量多品种与批量订单均可灵活承接。</t>
+  </si>
+  <si>
+    <t>主要设备 / 加工精度 / 适用材质 / 交付形式</t>
+  </si>
+  <si>
+    <t>车间概貌 · 搓牙车间</t>
+  </si>
+  <si>
+    <t>搓牙车间 / THREAD ROLLING WORKSHOP</t>
+  </si>
+  <si>
+    <t>通过搓丝机对工件进行螺纹滚压成型，牙型饱满、表面光洁，螺纹强度较切削加工显著提升，适合大批量标准紧固件的稳定生产。</t>
+  </si>
+  <si>
+    <t>主要设备 / 螺纹范围 / 日产能 / 检测方式</t>
+  </si>
+  <si>
+    <t>车间概貌 · 光学筛选车间</t>
+  </si>
+  <si>
+    <t>光学筛选车间 / OPTICAL SORTING WORKSHOP</t>
+  </si>
+  <si>
+    <t>采用光学影像筛选设备对产品进行全检，自动剔除尺寸超差、混料、毛刺、缺料等不良品，为出货品质提供最后一道保障。</t>
+  </si>
+  <si>
+    <t>主要设备 / 筛选项目 / 筛选速度 / 质量目标</t>
+  </si>
+  <si>
+    <t>车间概貌 · 底部号召区</t>
+  </si>
+  <si>
+    <t>欢迎实地考察我们的产线 / 如需了解设备清单、产能排期或安排样品试制，欢迎随时联系我们。 / 联系我们</t>
+  </si>
+  <si>
+    <t>联系我们 · 页首</t>
+  </si>
+  <si>
+    <t>无论是产品询价、定制开发还是商务合作，欢迎随时与我们取得联系。</t>
+  </si>
+  <si>
+    <t>联系我们 · 联系方式</t>
+  </si>
+  <si>
+    <t>公司地址（已填真实地址）</t>
+  </si>
+  <si>
+    <t>广东省中山市三乡镇第二工业区皇冠路5号8栋之A区</t>
+  </si>
+  <si>
+    <t>如需微调请在此列覆盖</t>
+  </si>
+  <si>
+    <t>联系电话（已填真实号码）</t>
+  </si>
+  <si>
+    <t>139 2818 0479（可点击拨打）</t>
+  </si>
+  <si>
+    <t>如需更换请覆盖</t>
+  </si>
+  <si>
+    <t>电子邮箱（务必真实）</t>
+  </si>
+  <si>
+    <t>info@sicen-hardware.com（占位）</t>
+  </si>
+  <si>
+    <t>真实邮箱</t>
+  </si>
+  <si>
+    <t>工作时间</t>
+  </si>
+  <si>
+    <t>周一至周六 8:30 – 18:00</t>
+  </si>
+  <si>
+    <t>联系我们 · 留言表单</t>
+  </si>
+  <si>
+    <t>表单下方说明</t>
+  </si>
+  <si>
+    <t>（演示占位表单，尚未接入后端；上线后可对接邮件或表单服务）</t>
+  </si>
+  <si>
+    <t>联系我们 · 地图</t>
+  </si>
+  <si>
+    <t>区块说明 / 地址</t>
+  </si>
+  <si>
+    <t>公司位置（地址已填真实）：广东省中山市三乡镇第二工业区皇冠路5号8栋之A区；提供高德/百度一键导航按钮</t>
+  </si>
+  <si>
+    <t>页脚</t>
+  </si>
+  <si>
+    <t>公司简介（3 行内）</t>
+  </si>
+  <si>
+    <t>思晨五金制品有限公司专注于精密五金制品的研发、制造与交付，以严谨的工艺与稳定的品质，为全球工业客户提供可靠的解决方案。</t>
+  </si>
+  <si>
+    <t>版权行英文全称</t>
+  </si>
+  <si>
+    <t>SICEN HARDWARE PRODUCTS CO., LTD.（请确认为营业执照英文名）</t>
+  </si>
+  <si>
+    <t>英文全称</t>
+  </si>
+  <si>
+    <t>ICP 备案号（必填，法规要求）</t>
+  </si>
+  <si>
+    <t>（待填，例如：粤ICP备2025XXXXXX号）</t>
+  </si>
+  <si>
+    <t>备案号</t>
+  </si>
+  <si>
+    <t>公安备案号（ICP 通过后 30 日内办理）</t>
+  </si>
+  <si>
+    <t>（待填，例如：粤公网安备XXXXXXXX号）</t>
+  </si>
+  <si>
+    <t>SEO · 首页</t>
+  </si>
+  <si>
+    <t>浏览器标题（title）</t>
+  </si>
+  <si>
+    <t>思晨五金制品有限公司 · 精密五金制造</t>
+  </si>
+  <si>
+    <t>20~30 字</t>
+  </si>
+  <si>
+    <t>页面描述（description）</t>
+  </si>
+  <si>
+    <t>思晨五金制品有限公司——精密冲压件、精密CNC加工件、紧固件、钣金件等五金制品研发、制造与交付，服务全球工业客户。</t>
+  </si>
+  <si>
+    <t>60~120 字</t>
+  </si>
+  <si>
+    <t>SEO · 关于我们</t>
+  </si>
+  <si>
+    <t>标题 / 描述</t>
+  </si>
+  <si>
+    <t>关于我们 / 了解思晨五金制品有限公司——公司简介、发展历程、企业文化与资质荣誉。</t>
+  </si>
+  <si>
+    <t>描述 60~120 字</t>
+  </si>
+  <si>
+    <t>SEO · 产品中心</t>
+  </si>
+  <si>
+    <t>产品中心 / 思晨五金产品中心——精密冲压件、精密CNC加工件、紧固件、钣金件、模具设计与表面处理服务。</t>
+  </si>
+  <si>
+    <t>SEO · 车间概貌</t>
+  </si>
+  <si>
+    <t>车间概貌 / 思晨五金车间概貌——冷镦车间、CNC 车间、搓牙车间、光学筛选车间，覆盖从成型到全检的完整五金制造工序。</t>
+  </si>
+  <si>
+    <t>SEO · 联系我们</t>
+  </si>
+  <si>
+    <t>联系我们 / 联系思晨五金制品有限公司——欢迎咨询产品、询价与合作。</t>
+  </si>
+  <si>
+    <t>company（公司）</t>
+  </si>
+  <si>
+    <t>slider-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 首页轮播图【第 1 张】厂区外景</t>
+  </si>
+  <si>
+    <t>1600px</t>
+  </si>
+  <si>
+    <t>slider-2.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 首页轮播图【第 2 张】生产车间全景</t>
+  </si>
+  <si>
+    <t>slider-3.png</t>
+  </si>
+  <si>
+    <t>首页 · 公司概貌轮播图【第 3 张】办公与展厅（待替换）</t>
+  </si>
+  <si>
+    <t>1600×900</t>
+  </si>
+  <si>
+    <t>slider-4.png</t>
+  </si>
+  <si>
+    <t>首页 · 公司概貌轮播图【第 4 张】团队与品质（待替换）</t>
+  </si>
+  <si>
+    <t>facade.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 公司外景 / 办公环境</t>
+  </si>
+  <si>
+    <t>office-1.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 公司风采（办公与展厅）</t>
+  </si>
+  <si>
+    <t>1200×900</t>
+  </si>
+  <si>
+    <t>team-1.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 公司风采（团队合影）</t>
+  </si>
+  <si>
+    <t>map-1.png</t>
+  </si>
+  <si>
+    <t>联系我们 · 公司位置示意图（可换成地图 App 位置截图）</t>
+  </si>
+  <si>
+    <t>1920×800</t>
+  </si>
+  <si>
+    <t>equipment（器械设备）</t>
+  </si>
+  <si>
+    <t>hero.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 首页首屏大图</t>
+  </si>
+  <si>
+    <t>1920px</t>
+  </si>
+  <si>
+    <t>workshop-1.png</t>
+  </si>
+  <si>
+    <t>首页 · 制造实力全宽横幅</t>
+  </si>
+  <si>
+    <t>workshop-stamping.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 工厂与设备（冲压车间）</t>
+  </si>
+  <si>
+    <t>workshop-cnc.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 工厂与设备（CNC 车间）</t>
+  </si>
+  <si>
+    <t>lab-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（品质检测中心）</t>
+  </si>
+  <si>
+    <t>1400px</t>
+  </si>
+  <si>
+    <t>machine-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（生产设备 1）</t>
+  </si>
+  <si>
+    <t>machine-2.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（生产设备 2）</t>
+  </si>
+  <si>
+    <t>qc-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 关于我们 · 工厂与设备（品质管控）</t>
+  </si>
+  <si>
+    <t>warehouse-1.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 工厂与设备（仓储物流，待替换）</t>
+  </si>
+  <si>
+    <t>products（产品）</t>
+  </si>
+  <si>
+    <t>stamping-1.png</t>
+  </si>
+  <si>
+    <t>产品 1：精密冲压件（首页卡片 + 产品中心）</t>
+  </si>
+  <si>
+    <t>machining-1.png</t>
+  </si>
+  <si>
+    <t>产品 2：精密 CNC 加工件</t>
+  </si>
+  <si>
+    <t>fasteners-1.png</t>
+  </si>
+  <si>
+    <t>产品 3：紧固件与连接件</t>
+  </si>
+  <si>
+    <t>sheet-metal-1.png</t>
+  </si>
+  <si>
+    <t>产品 4：钣金件</t>
+  </si>
+  <si>
+    <t>spring-1.png</t>
+  </si>
+  <si>
+    <t>产品 5：弹簧与弹片</t>
+  </si>
+  <si>
+    <t>turning-1.png</t>
+  </si>
+  <si>
+    <t>产品 6：精密车削件</t>
+  </si>
+  <si>
+    <t>mold-1.png</t>
+  </si>
+  <si>
+    <t>产品 7：模具设计与制造</t>
+  </si>
+  <si>
+    <t>finishing-1.png</t>
+  </si>
+  <si>
+    <t>产品 8：表面处理服务（首页卡片 + 产品中心）</t>
+  </si>
+  <si>
+    <t>gallery-1.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 1 张</t>
+  </si>
+  <si>
+    <t>gallery-2.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 2 张</t>
+  </si>
+  <si>
+    <t>gallery-3.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 3 张</t>
+  </si>
+  <si>
+    <t>gallery-4.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 4 张</t>
+  </si>
+  <si>
+    <t>gallery-5.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 5 张</t>
+  </si>
+  <si>
+    <t>gallery-6.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 6 张</t>
+  </si>
+  <si>
+    <t>gallery-7.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 7 张</t>
+  </si>
+  <si>
+    <t>gallery-8.png</t>
+  </si>
+  <si>
+    <t>产品中心 · 产品实拍图集 第 8 张</t>
+  </si>
+  <si>
+    <t>certificates（认证）</t>
+  </si>
+  <si>
+    <t>cert-1.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 证书展示 第 1 张（如 ISO9001）</t>
+  </si>
+  <si>
+    <t>cert-2.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 证书展示 第 2 张（如 ISO14001）</t>
+  </si>
+  <si>
+    <t>cert-3.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 证书展示 第 3 张（如 高新技术企业）</t>
+  </si>
+  <si>
+    <t>cert-4.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 证书展示 第 4 张</t>
+  </si>
+  <si>
+    <t>cert-5.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 证书展示 第 5 张</t>
+  </si>
+  <si>
+    <t>cert-6.png</t>
+  </si>
+  <si>
+    <t>关于我们 · 证书展示 第 6 张</t>
+  </si>
+  <si>
+    <t>workshops（车间）</t>
+  </si>
+  <si>
+    <t>cold-heading-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 车间概貌 · 冷镦车间【大图】</t>
+  </si>
+  <si>
+    <t>cold-heading-2.png</t>
+  </si>
+  <si>
+    <t>冷镦车间 · 细节图 1（待替换）</t>
+  </si>
+  <si>
+    <t>cold-heading-3.png</t>
+  </si>
+  <si>
+    <t>冷镦车间 · 细节图 2（待替换）</t>
+  </si>
+  <si>
+    <t>cnc-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 车间概貌 · CNC 车间【大图】</t>
+  </si>
+  <si>
+    <t>cnc-2.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · CNC 车间 · 细节图 1</t>
+  </si>
+  <si>
+    <t>1200px</t>
+  </si>
+  <si>
+    <t>cnc-3.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · CNC 车间 · 细节图 2</t>
+  </si>
+  <si>
+    <t>thread-rolling-1.png</t>
+  </si>
+  <si>
+    <t>车间概貌 · 搓牙车间【大图】（待替换）</t>
+  </si>
+  <si>
+    <t>thread-rolling-2.png</t>
+  </si>
+  <si>
+    <t>搓牙车间 · 细节图 1（待替换）</t>
+  </si>
+  <si>
+    <t>thread-rolling-3.png</t>
+  </si>
+  <si>
+    <t>搓牙车间 · 细节图 2（待替换）</t>
+  </si>
+  <si>
+    <t>optical-sorting-1.jpg</t>
+  </si>
+  <si>
+    <t>✅已替换 · 车间概貌 · 光学筛选车间【大图】</t>
+  </si>
+  <si>
+    <t>optical-sorting-2.png</t>
+  </si>
+  <si>
+    <t>光学筛选车间 · 细节图 1（待替换）</t>
+  </si>
+  <si>
+    <t>optical-sorting-3.png</t>
+  </si>
+  <si>
+    <t>光学筛选车间 · 细节图 2（待替换）</t>
+  </si>
+  <si>
+    <t>提示：直接把真实图片按"文件名"放入对应目录覆盖即可，无需改动代码。</t>
+  </si>
+  <si>
     <t>车间概貌 / 冷镦、CNC、搓牙、光学筛选四大车间，覆盖从毛坯成型到全检出货的完整工序。</t>
-  </si>
-  <si>
-    <t>副标题 30~60 字</t>
-  </si>
-  <si>
-    <t>车间概貌 · 冷镦车间</t>
-  </si>
-  <si>
-    <t>标题 / 英文标</t>
-  </si>
-  <si>
-    <t>冷镦车间 / COLD HEADING WORKSHOP</t>
-  </si>
-  <si>
-    <t>车间描述</t>
-  </si>
-  <si>
-    <t>采用多工位冷镦成型工艺，从盘料一次成型螺栓、螺母及各类异形件。材料利用率高、生产效率快，金属流线连续不断，产品强度与一致性明显优于切削加工。</t>
-  </si>
-  <si>
-    <t>参数 1~4：标签 / 内容（现均为占位）</t>
-  </si>
-  <si>
-    <t>主要设备 / 加工范围 / 日产能 / 品质管控</t>
-  </si>
-  <si>
-    <t>每项 10~30 字</t>
-  </si>
-  <si>
-    <t>车间概貌 · CNC 车间</t>
-  </si>
-  <si>
-    <t>CNC 车间 / CNC MACHINING WORKSHOP</t>
-  </si>
-  <si>
-    <t>配置数控车床与加工中心，支持车铣复合加工，适合结构复杂、公差要求严格的产品；小批量多品种与批量订单均可灵活承接。</t>
-  </si>
-  <si>
-    <t>主要设备 / 加工精度 / 适用材质 / 交付形式</t>
-  </si>
-  <si>
-    <t>车间概貌 · 搓牙车间</t>
-  </si>
-  <si>
-    <t>搓牙车间 / THREAD ROLLING WORKSHOP</t>
-  </si>
-  <si>
-    <t>通过搓丝机对工件进行螺纹滚压成型，牙型饱满、表面光洁，螺纹强度较切削加工显著提升，适合大批量标准紧固件的稳定生产。</t>
-  </si>
-  <si>
-    <t>主要设备 / 螺纹范围 / 日产能 / 检测方式</t>
-  </si>
-  <si>
-    <t>车间概貌 · 光学筛选车间</t>
-  </si>
-  <si>
-    <t>光学筛选车间 / OPTICAL SORTING WORKSHOP</t>
-  </si>
-  <si>
-    <t>采用光学影像筛选设备对产品进行全检，自动剔除尺寸超差、混料、毛刺、缺料等不良品，为出货品质提供最后一道保障。</t>
-  </si>
-  <si>
-    <t>主要设备 / 筛选项目 / 筛选速度 / 质量目标</t>
-  </si>
-  <si>
-    <t>车间概貌 · 底部号召区</t>
-  </si>
-  <si>
-    <t>欢迎实地考察我们的产线 / 如需了解设备清单、产能排期或安排样品试制，欢迎随时联系我们。 / 联系我们</t>
-  </si>
-  <si>
-    <t>联系我们 · 页首</t>
-  </si>
-  <si>
-    <t>无论是产品询价、定制开发还是商务合作，欢迎随时与我们取得联系。</t>
-  </si>
-  <si>
-    <t>联系我们 · 联系方式</t>
-  </si>
-  <si>
-    <t>公司地址（已填真实地址）</t>
-  </si>
-  <si>
-    <t>广东省中山市三乡镇第二工业区皇冠路5号8栋之A区</t>
-  </si>
-  <si>
-    <t>如需微调请在此列覆盖</t>
-  </si>
-  <si>
-    <t>联系电话（已填真实号码）</t>
-  </si>
-  <si>
-    <t>139 2818 0479（可点击拨打）</t>
-  </si>
-  <si>
-    <t>如需更换请覆盖</t>
-  </si>
-  <si>
-    <t>电子邮箱（务必真实）</t>
-  </si>
-  <si>
-    <t>info@sicen-hardware.com（占位）</t>
-  </si>
-  <si>
-    <t>真实邮箱</t>
-  </si>
-  <si>
-    <t>工作时间</t>
-  </si>
-  <si>
-    <t>周一至周六 8:30 – 18:00</t>
-  </si>
-  <si>
-    <t>联系我们 · 留言表单</t>
-  </si>
-  <si>
-    <t>表单下方说明</t>
-  </si>
-  <si>
-    <t>（演示占位表单，尚未接入后端；上线后可对接邮件或表单服务）</t>
-  </si>
-  <si>
-    <t>联系我们 · 地图</t>
-  </si>
-  <si>
-    <t>区块说明 / 地址</t>
-  </si>
-  <si>
-    <t>公司位置（地址已填真实）：广东省中山市三乡镇第二工业区皇冠路5号8栋之A区；提供高德/百度一键导航按钮</t>
-  </si>
-  <si>
-    <t>页脚</t>
-  </si>
-  <si>
-    <t>公司简介（3 行内）</t>
-  </si>
-  <si>
-    <t>思晨五金制品有限公司专注于精密五金制品的研发、制造与交付，以严谨的工艺与稳定的品质，为全球工业客户提供可靠的解决方案。</t>
-  </si>
-  <si>
-    <t>版权行英文全称</t>
-  </si>
-  <si>
-    <t>SICEN HARDWARE PRODUCTS CO., LTD.（请确认为营业执照英文名）</t>
-  </si>
-  <si>
-    <t>英文全称</t>
-  </si>
-  <si>
-    <t>ICP 备案号（必填，法规要求）</t>
-  </si>
-  <si>
-    <t>（待填，例如：粤ICP备2025XXXXXX号）</t>
-  </si>
-  <si>
-    <t>备案号</t>
-  </si>
-  <si>
-    <t>公安备案号（ICP 通过后 30 日内办理）</t>
-  </si>
-  <si>
-    <t>（待填，例如：粤公网安备XXXXXXXX号）</t>
-  </si>
-  <si>
-    <t>SEO · 首页</t>
-  </si>
-  <si>
-    <t>浏览器标题（title）</t>
-  </si>
-  <si>
-    <t>思晨五金制品有限公司 · 精密五金制造</t>
-  </si>
-  <si>
-    <t>20~30 字</t>
-  </si>
-  <si>
-    <t>页面描述（description）</t>
-  </si>
-  <si>
-    <t>思晨五金制品有限公司——精密冲压件、精密CNC加工件、紧固件、钣金件等五金制品研发、制造与交付，服务全球工业客户。</t>
-  </si>
-  <si>
-    <t>60~120 字</t>
-  </si>
-  <si>
-    <t>SEO · 关于我们</t>
-  </si>
-  <si>
-    <t>标题 / 描述</t>
-  </si>
-  <si>
-    <t>关于我们 / 了解思晨五金制品有限公司——公司简介、发展历程、企业文化与资质荣誉。</t>
-  </si>
-  <si>
-    <t>描述 60~120 字</t>
-  </si>
-  <si>
-    <t>SEO · 产品中心</t>
-  </si>
-  <si>
-    <t>产品中心 / 思晨五金产品中心——精密冲压件、精密CNC加工件、紧固件、钣金件、模具设计与表面处理服务。</t>
-  </si>
-  <si>
-    <t>SEO · 车间概貌</t>
-  </si>
-  <si>
-    <t>车间概貌 / 思晨五金车间概貌——冷镦车间、CNC 车间、搓牙车间、光学筛选车间，覆盖从成型到全检的完整五金制造工序。</t>
-  </si>
-  <si>
-    <t>SEO · 联系我们</t>
-  </si>
-  <si>
-    <t>联系我们 / 联系思晨五金制品有限公司——欢迎咨询产品、询价与合作。</t>
-  </si>
-  <si>
-    <t>company（公司）</t>
-  </si>
-  <si>
-    <t>slider-1.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 首页轮播图【第 1 张】厂区外景</t>
-  </si>
-  <si>
-    <t>1600px</t>
-  </si>
-  <si>
-    <t>slider-2.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 首页轮播图【第 2 张】生产车间全景</t>
-  </si>
-  <si>
-    <t>slider-3.png</t>
-  </si>
-  <si>
-    <t>首页 · 公司概貌轮播图【第 3 张】办公与展厅（待替换）</t>
-  </si>
-  <si>
-    <t>1600×900</t>
-  </si>
-  <si>
-    <t>slider-4.png</t>
-  </si>
-  <si>
-    <t>首页 · 公司概貌轮播图【第 4 张】团队与品质（待替换）</t>
-  </si>
-  <si>
-    <t>facade.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 关于我们 · 公司外景 / 办公环境</t>
-  </si>
-  <si>
-    <t>office-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 公司风采（办公与展厅）</t>
-  </si>
-  <si>
-    <t>1200×900</t>
-  </si>
-  <si>
-    <t>team-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 公司风采（团队合影）</t>
-  </si>
-  <si>
-    <t>map-1.png</t>
-  </si>
-  <si>
-    <t>联系我们 · 公司位置示意图（可换成地图 App 位置截图）</t>
-  </si>
-  <si>
-    <t>1920×800</t>
-  </si>
-  <si>
-    <t>equipment（器械设备）</t>
-  </si>
-  <si>
-    <t>hero.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 首页首屏大图</t>
-  </si>
-  <si>
-    <t>1920px</t>
-  </si>
-  <si>
-    <t>workshop-1.png</t>
-  </si>
-  <si>
-    <t>首页 · 制造实力全宽横幅</t>
-  </si>
-  <si>
-    <t>workshop-stamping.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 工厂与设备（冲压车间）</t>
-  </si>
-  <si>
-    <t>workshop-cnc.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 工厂与设备（CNC 车间）</t>
-  </si>
-  <si>
-    <t>lab-1.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 关于我们 · 工厂与设备（品质检测中心）</t>
-  </si>
-  <si>
-    <t>1400px</t>
-  </si>
-  <si>
-    <t>machine-1.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 关于我们 · 工厂与设备（生产设备 1）</t>
-  </si>
-  <si>
-    <t>machine-2.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 关于我们 · 工厂与设备（生产设备 2）</t>
-  </si>
-  <si>
-    <t>qc-1.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 关于我们 · 工厂与设备（品质管控）</t>
-  </si>
-  <si>
-    <t>warehouse-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 工厂与设备（仓储物流，待替换）</t>
-  </si>
-  <si>
-    <t>products（产品）</t>
-  </si>
-  <si>
-    <t>stamping-1.png</t>
-  </si>
-  <si>
-    <t>产品 1：精密冲压件（首页卡片 + 产品中心）</t>
-  </si>
-  <si>
-    <t>machining-1.png</t>
-  </si>
-  <si>
-    <t>产品 2：精密 CNC 加工件</t>
-  </si>
-  <si>
-    <t>fasteners-1.png</t>
-  </si>
-  <si>
-    <t>产品 3：紧固件与连接件</t>
-  </si>
-  <si>
-    <t>sheet-metal-1.png</t>
-  </si>
-  <si>
-    <t>产品 4：钣金件</t>
-  </si>
-  <si>
-    <t>spring-1.png</t>
-  </si>
-  <si>
-    <t>产品 5：弹簧与弹片</t>
-  </si>
-  <si>
-    <t>turning-1.png</t>
-  </si>
-  <si>
-    <t>产品 6：精密车削件</t>
-  </si>
-  <si>
-    <t>mold-1.png</t>
-  </si>
-  <si>
-    <t>产品 7：模具设计与制造</t>
-  </si>
-  <si>
-    <t>finishing-1.png</t>
-  </si>
-  <si>
-    <t>产品 8：表面处理服务（首页卡片 + 产品中心）</t>
-  </si>
-  <si>
-    <t>gallery-1.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 1 张</t>
-  </si>
-  <si>
-    <t>gallery-2.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 2 张</t>
-  </si>
-  <si>
-    <t>gallery-3.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 3 张</t>
-  </si>
-  <si>
-    <t>gallery-4.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 4 张</t>
-  </si>
-  <si>
-    <t>gallery-5.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 5 张</t>
-  </si>
-  <si>
-    <t>gallery-6.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 6 张</t>
-  </si>
-  <si>
-    <t>gallery-7.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 7 张</t>
-  </si>
-  <si>
-    <t>gallery-8.png</t>
-  </si>
-  <si>
-    <t>产品中心 · 产品实拍图集 第 8 张</t>
-  </si>
-  <si>
-    <t>certificates（认证）</t>
-  </si>
-  <si>
-    <t>cert-1.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 证书展示 第 1 张（如 ISO9001）</t>
-  </si>
-  <si>
-    <t>cert-2.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 证书展示 第 2 张（如 ISO14001）</t>
-  </si>
-  <si>
-    <t>cert-3.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 证书展示 第 3 张（如 高新技术企业）</t>
-  </si>
-  <si>
-    <t>cert-4.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 证书展示 第 4 张</t>
-  </si>
-  <si>
-    <t>cert-5.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 证书展示 第 5 张</t>
-  </si>
-  <si>
-    <t>cert-6.png</t>
-  </si>
-  <si>
-    <t>关于我们 · 证书展示 第 6 张</t>
-  </si>
-  <si>
-    <t>workshops（车间）</t>
-  </si>
-  <si>
-    <t>cold-heading-1.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 车间概貌 · 冷镦车间【大图】</t>
-  </si>
-  <si>
-    <t>cold-heading-2.png</t>
-  </si>
-  <si>
-    <t>冷镦车间 · 细节图 1（待替换）</t>
-  </si>
-  <si>
-    <t>cold-heading-3.png</t>
-  </si>
-  <si>
-    <t>冷镦车间 · 细节图 2（待替换）</t>
-  </si>
-  <si>
-    <t>cnc-1.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 车间概貌 · CNC 车间【大图】</t>
-  </si>
-  <si>
-    <t>cnc-2.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · CNC 车间 · 细节图 1</t>
-  </si>
-  <si>
-    <t>1200px</t>
-  </si>
-  <si>
-    <t>cnc-3.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · CNC 车间 · 细节图 2</t>
-  </si>
-  <si>
-    <t>thread-rolling-1.png</t>
-  </si>
-  <si>
-    <t>车间概貌 · 搓牙车间【大图】（待替换）</t>
-  </si>
-  <si>
-    <t>thread-rolling-2.png</t>
-  </si>
-  <si>
-    <t>搓牙车间 · 细节图 1（待替换）</t>
-  </si>
-  <si>
-    <t>thread-rolling-3.png</t>
-  </si>
-  <si>
-    <t>搓牙车间 · 细节图 2（待替换）</t>
-  </si>
-  <si>
-    <t>optical-sorting-1.jpg</t>
-  </si>
-  <si>
-    <t>✅已替换 · 车间概貌 · 光学筛选车间【大图】</t>
-  </si>
-  <si>
-    <t>optical-sorting-2.png</t>
-  </si>
-  <si>
-    <t>光学筛选车间 · 细节图 1（待替换）</t>
-  </si>
-  <si>
-    <t>optical-sorting-3.png</t>
-  </si>
-  <si>
-    <t>光学筛选车间 · 细节图 2（待替换）</t>
-  </si>
-  <si>
-    <t>提示：直接把真实图片按"文件名"放入对应目录覆盖即可，无需改动代码。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF7A7A7A"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1269,7 +1292,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1605,15 +1628,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1629,7 +1652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1637,7 +1660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1645,7 +1668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1653,7 +1676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1661,7 +1684,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1669,7 +1692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1677,7 +1700,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1685,7 +1708,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1693,7 +1716,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1701,24 +1724,25 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1728,7 +1752,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -1788,7 +1812,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1848,7 +1872,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1868,7 +1892,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1888,7 +1912,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1908,7 +1932,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1928,7 +1952,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1948,7 +1972,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1968,7 +1992,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1988,7 +2012,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2008,7 +2032,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2028,7 +2052,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2048,7 +2072,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2068,7 +2092,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2088,7 +2112,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2108,7 +2132,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2128,7 +2152,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2148,7 +2172,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2168,7 +2192,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2188,7 +2212,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2228,7 +2252,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2248,7 +2272,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2268,7 +2292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2288,7 +2312,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2308,7 +2332,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2328,7 +2352,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2349,18 +2373,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2370,7 +2395,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -2390,7 +2415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2410,7 +2435,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2430,7 +2455,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2450,7 +2475,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2470,7 +2495,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2490,7 +2515,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2510,7 +2535,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2530,7 +2555,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2550,7 +2575,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2570,7 +2595,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2590,7 +2615,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2610,7 +2635,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2630,7 +2655,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2650,7 +2675,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2670,7 +2695,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2690,7 +2715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2710,7 +2735,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2730,7 +2755,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2750,7 +2775,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2770,7 +2795,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2791,18 +2816,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2812,7 +2838,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -2832,7 +2858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2852,7 +2878,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2872,7 +2898,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2892,7 +2918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2912,7 +2938,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2932,7 +2958,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2952,7 +2978,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2972,7 +2998,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2992,7 +3018,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3012,7 +3038,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -3032,7 +3058,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3052,7 +3078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -3072,7 +3098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3092,7 +3118,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3112,7 +3138,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3132,7 +3158,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3153,18 +3179,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3174,7 +3201,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -3194,7 +3221,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3205,27 +3232,27 @@
         <v>203</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="F2" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>165</v>
@@ -3234,18 +3261,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>51</v>
@@ -3254,38 +3281,38 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>165</v>
@@ -3294,18 +3321,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
@@ -3314,38 +3341,38 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>165</v>
@@ -3354,18 +3381,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>51</v>
@@ -3374,38 +3401,38 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>165</v>
@@ -3414,18 +3441,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>51</v>
@@ -3434,38 +3461,38 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>115</v>
@@ -3475,18 +3502,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3496,7 +3524,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -3516,18 +3544,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>170</v>
@@ -3536,78 +3564,78 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="F3" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>165</v>
@@ -3616,18 +3644,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>170</v>
@@ -3636,18 +3664,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>170</v>
@@ -3656,18 +3684,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>54</v>
@@ -3676,79 +3704,80 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="F11" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3758,7 +3787,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -3783,134 +3812,135 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="F2" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="F3" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3920,7 +3950,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -3945,16 +3975,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>33</v>
@@ -3965,56 +3995,56 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
@@ -4025,16 +4055,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -4045,16 +4075,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>33</v>
@@ -4065,216 +4095,216 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="F9" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>309</v>
-      </c>
       <c r="F14" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>33</v>
@@ -4285,16 +4315,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>33</v>
@@ -4305,16 +4335,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>33</v>
@@ -4325,16 +4355,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
@@ -4345,16 +4375,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -4365,16 +4395,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>33</v>
@@ -4385,16 +4415,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>33</v>
@@ -4405,16 +4435,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>33</v>
@@ -4425,16 +4455,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>33</v>
@@ -4445,16 +4475,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>33</v>
@@ -4465,16 +4495,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>33</v>
@@ -4485,16 +4515,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>33</v>
@@ -4505,16 +4535,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -4525,16 +4555,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
@@ -4545,16 +4575,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
@@ -4565,16 +4595,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>33</v>
@@ -4585,136 +4615,136 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="E39" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -4725,16 +4755,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>33</v>
@@ -4745,16 +4775,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="E42" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>33</v>
@@ -4765,16 +4795,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="E43" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>33</v>
@@ -4785,16 +4815,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>33</v>
@@ -4805,16 +4835,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>33</v>
@@ -4825,148 +4855,149 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>377</v>
-      </c>
       <c r="E46" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>379</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="E49" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="E51" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>390</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>